--- a/originales/respuestas/2025/01. Calificadas/bucle p35/Subred Integrada De Servicios De Salud Norte.xlsx
+++ b/originales/respuestas/2025/01. Calificadas/bucle p35/Subred Integrada De Servicios De Salud Norte.xlsx
@@ -9,14 +9,14 @@
   <calcPr/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="tGjl83zK0LoUOFkLo1u+8qyEXolauroFp3qNce/upek="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="lo/kRU2pYxwCUh89+o5yzW77jJQANR2ZC9yiC4eMpi8="/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="47">
   <si>
     <t>Entidad</t>
   </si>
@@ -150,30 +150,18 @@
     <t>https://innovebogota.veeduriadistrital.gov.co:4282/app/api_preguntas/public/api/download-file-by-nombre/208/Proceso_Gestion_del_Conocimiento (1).pdf</t>
   </si>
   <si>
-    <t>Procedimiento Gestión del Conocimiento</t>
-  </si>
-  <si>
-    <t>Se describe la caracterización del proceso de gestión del conocimiento y la innovación el cual pertenece al macroproceso estratégico dentro del mapa de procesos de la entidad.</t>
-  </si>
-  <si>
-    <t>https://innovebogota.veeduriadistrital.gov.co:4282/app/api_preguntas/public/api/download-file-by-nombre/208/Procedimiento Gestión del Conocimiento.pdf</t>
-  </si>
-  <si>
     <t>Programa</t>
   </si>
   <si>
     <t>CENTRO DE INVESTIGACIÓN CIS NORTE</t>
-  </si>
-  <si>
-    <t>Se describe el procedimiento de Gestión del Conocimiento,</t>
-  </si>
-  <si>
-    <t>https://innovebogota.veeduriadistrital.gov.co:4282/app/api_preguntas/public/api/download-file-by-nombre/208/CISNORTE - Investigación - Innovación.pdf</t>
   </si>
   <si>
     <t>El Centro de Investigación de la Subred Norte CISNORTE, hace parte de la Oficina de Gestión del Conocimiento, fue creado mediante Resolución 628 de 2020.
  El propósito de CISNORTE es apoyar la investigación en salud y la transferencia de conocimiento en la entidad. 
  También, facilita la orientación y desarrollo de propuestas de investigación, formación de estudiantes y contribuye al avance del conocimiento en salud, para ello, cuenta con profesionales especializados en diferentes áreas de la salud y con capacidades en laboratorio clínico, farmacia, biología molecular e imágenes diagnósticas.</t>
+  </si>
+  <si>
+    <t>https://innovebogota.veeduriadistrital.gov.co:4282/app/api_preguntas/public/api/download-file-by-nombre/208/CISNORTE - Investigación - Innovación.pdf</t>
   </si>
 </sst>
 </file>
@@ -859,16 +847,16 @@
         <v>16</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F8" s="4" t="s">
         <v>20</v>
@@ -902,96 +890,8 @@
       </c>
       <c r="P8" s="4"/>
     </row>
-    <row r="9" ht="14.25" customHeight="1">
-      <c r="A9" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="D9" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="E9" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="F9" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="G9" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="H9" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="I9" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="J9" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="K9" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="L9" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="M9" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="N9" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="O9" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="P9" s="4"/>
-    </row>
-    <row r="10" ht="14.25" customHeight="1">
-      <c r="A10" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="B10" s="4"/>
-      <c r="C10" s="4"/>
-      <c r="D10" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="E10" s="4"/>
-      <c r="F10" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="G10" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="H10" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="I10" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="J10" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="K10" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="L10" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="M10" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="N10" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="O10" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="P10" s="4"/>
-    </row>
+    <row r="9" ht="14.25" customHeight="1"/>
+    <row r="10" ht="14.25" customHeight="1"/>
     <row r="11" ht="14.25" customHeight="1"/>
     <row r="12" ht="14.25" customHeight="1"/>
     <row r="13" ht="14.25" customHeight="1"/>
@@ -1980,8 +1880,6 @@
     <row r="996" ht="14.25" customHeight="1"/>
     <row r="997" ht="14.25" customHeight="1"/>
     <row r="998" ht="14.25" customHeight="1"/>
-    <row r="999" ht="14.25" customHeight="1"/>
-    <row r="1000" ht="14.25" customHeight="1"/>
   </sheetData>
   <printOptions/>
   <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
